--- a/Pruebas calificadas/COLEGIO LAUREL DE CERA (IED)_1101_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO LAUREL DE CERA (IED)_1101_CALIFICADO.xlsx
@@ -7964,14 +7964,14 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V30" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="V30" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="Z30" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Z30" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -8217,14 +8217,14 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V31" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="V31" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
@@ -8234,12 +8234,12 @@
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="Z31" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Z31" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -8470,9 +8470,9 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V32" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="V32" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -8480,9 +8480,9 @@
           <t>B</t>
         </is>
       </c>
-      <c r="X32" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+      <c r="X32" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
@@ -8723,14 +8723,14 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V33" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="V33" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="Z33" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Z33" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -8976,14 +8976,14 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V34" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="V34" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
@@ -8993,12 +8993,12 @@
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="Z34" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Z34" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -9229,14 +9229,14 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V35" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="V35" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
@@ -9246,12 +9246,12 @@
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="Z35" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Z35" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
@@ -9482,14 +9482,14 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V36" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="V36" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
@@ -9499,12 +9499,12 @@
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="Z36" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Z36" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -9735,14 +9735,14 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V37" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="V37" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="Z37" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Z37" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -9988,14 +9988,14 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V38" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="V38" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
@@ -10005,12 +10005,12 @@
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="Z38" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Z38" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -10241,14 +10241,14 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V39" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="V39" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
@@ -10258,12 +10258,12 @@
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="Z39" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Z39" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -10494,14 +10494,14 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V40" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="V40" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
@@ -10511,12 +10511,12 @@
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="Z40" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Z40" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -10747,14 +10747,14 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V41" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="V41" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
@@ -10764,12 +10764,12 @@
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="Z41" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Z41" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -11000,29 +11000,29 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V42" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="V42" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X42" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X42" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
-        </is>
-      </c>
-      <c r="Y42" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="Z42" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+      <c r="Z42" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr"/>
@@ -11241,14 +11241,14 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V43" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="V43" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X43" s="3" t="inlineStr">
@@ -11258,12 +11258,12 @@
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="Z43" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Z43" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -11486,14 +11486,14 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V44" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="V44" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X44" s="3" t="inlineStr">
@@ -11503,12 +11503,12 @@
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="Z44" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Z44" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -11739,14 +11739,14 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V45" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="V45" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
@@ -11756,12 +11756,12 @@
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="Z45" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Z45" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -11992,14 +11992,14 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V46" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="V46" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X46" s="3" t="inlineStr">
@@ -12009,12 +12009,12 @@
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="Z46" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Z46" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -12245,14 +12245,14 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V47" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="V47" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X47" s="3" t="inlineStr">
@@ -12262,12 +12262,12 @@
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="Z47" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Z47" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
@@ -12498,14 +12498,14 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V48" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="V48" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X48" s="3" t="inlineStr">
@@ -12515,12 +12515,12 @@
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="Z48" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Z48" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -12751,14 +12751,14 @@
           <t>A</t>
         </is>
       </c>
-      <c r="V49" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+      <c r="V49" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X49" s="3" t="inlineStr">
@@ -12768,12 +12768,12 @@
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="Z49" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Z49" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
@@ -13011,7 +13011,7 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X50" s="3" t="inlineStr">
@@ -13021,7 +13021,7 @@
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Z50" s="3" t="inlineStr">
@@ -13257,14 +13257,14 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V51" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="V51" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X51" s="3" t="inlineStr">
@@ -13274,12 +13274,12 @@
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="Z51" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Z51" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
@@ -13510,24 +13510,24 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V52" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="V52" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="X52" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X52" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Z52" s="3" t="inlineStr">
@@ -13763,29 +13763,29 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V53" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="V53" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X53" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X53" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
-        </is>
-      </c>
-      <c r="Y53" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="Z53" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+      <c r="Z53" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
@@ -14016,29 +14016,29 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V54" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="V54" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X54" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X54" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
-        </is>
-      </c>
-      <c r="Y54" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="Z54" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+      <c r="Z54" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
@@ -14265,14 +14265,14 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V55" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="V55" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X55" s="3" t="inlineStr">
@@ -14282,7 +14282,7 @@
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Z55" s="3" t="inlineStr">
@@ -14518,14 +14518,14 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V56" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="V56" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X56" s="3" t="inlineStr">
@@ -14535,12 +14535,12 @@
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="Z56" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Z56" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
@@ -14771,14 +14771,14 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V57" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="V57" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X57" s="3" t="inlineStr">
@@ -14788,12 +14788,12 @@
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="Z57" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Z57" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">

--- a/Pruebas calificadas/COLEGIO LAUREL DE CERA (IED)_1101_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO LAUREL DE CERA (IED)_1101_CALIFICADO.xlsx
@@ -807,11 +807,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="inlineStr"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>111001800694</t>
@@ -1052,11 +1048,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t>111001800694</t>
@@ -1305,11 +1297,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>111001800694</t>
@@ -1558,11 +1546,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>111001800694</t>
@@ -1811,11 +1795,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="inlineStr"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
           <t>111001800694</t>
@@ -2064,11 +2044,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
           <t>111001800694</t>
@@ -2309,11 +2285,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
           <t>111001800694</t>
@@ -2554,11 +2526,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>111001800694</t>
@@ -2807,11 +2775,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t>111001800694</t>
@@ -3060,11 +3024,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
           <t>111001800694</t>
@@ -3313,11 +3273,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
           <t>111001800694</t>
@@ -3566,11 +3522,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="2" t="inlineStr">
         <is>
           <t>111001800694</t>
@@ -3819,11 +3771,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A14" s="2" t="inlineStr"/>
       <c r="B14" s="2" t="inlineStr">
         <is>
           <t>111001800694</t>
@@ -4072,11 +4020,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A15" s="2" t="inlineStr"/>
       <c r="B15" s="2" t="inlineStr">
         <is>
           <t>111001800694</t>
@@ -4325,11 +4269,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A16" s="2" t="inlineStr"/>
       <c r="B16" s="2" t="inlineStr">
         <is>
           <t>111001800694</t>
@@ -4578,11 +4518,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
           <t>111001800694</t>
@@ -4827,11 +4763,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A18" s="2" t="inlineStr"/>
       <c r="B18" s="2" t="inlineStr">
         <is>
           <t>111001800694</t>
@@ -5080,11 +5012,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="inlineStr"/>
       <c r="B19" s="2" t="inlineStr">
         <is>
           <t>111001800694</t>
@@ -5333,11 +5261,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="inlineStr"/>
       <c r="B20" s="2" t="inlineStr">
         <is>
           <t>111001800694</t>
@@ -5586,11 +5510,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
           <t>111001800694</t>
@@ -5839,11 +5759,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A22" s="2" t="inlineStr"/>
       <c r="B22" s="2" t="inlineStr">
         <is>
           <t>111001800694</t>
@@ -6092,11 +6008,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="inlineStr"/>
       <c r="B23" s="2" t="inlineStr">
         <is>
           <t>111001800694</t>
@@ -6345,11 +6257,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="2" t="inlineStr">
         <is>
           <t>111001800694</t>
@@ -6598,11 +6506,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A25" s="2" t="inlineStr"/>
       <c r="B25" s="2" t="inlineStr">
         <is>
           <t>111001800694</t>
@@ -6851,11 +6755,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
           <t>111001800694</t>
@@ -7104,11 +7004,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
           <t>111001800694</t>
@@ -7357,11 +7253,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A28" s="2" t="inlineStr"/>
       <c r="B28" s="2" t="inlineStr">
         <is>
           <t>111001800694</t>
@@ -7610,11 +7502,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="inlineStr"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
           <t>111001800694</t>
@@ -7863,11 +7751,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A30" s="2" t="inlineStr"/>
       <c r="B30" s="2" t="inlineStr">
         <is>
           <t>111001800694</t>
@@ -8116,11 +8000,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
           <t>111001800694</t>
@@ -8369,11 +8249,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="inlineStr"/>
       <c r="B32" s="2" t="inlineStr">
         <is>
           <t>111001800694</t>
@@ -8622,11 +8498,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A33" s="2" t="inlineStr"/>
       <c r="B33" s="2" t="inlineStr">
         <is>
           <t>111001800694</t>
@@ -8875,11 +8747,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A34" s="2" t="inlineStr"/>
       <c r="B34" s="2" t="inlineStr">
         <is>
           <t>111001800694</t>
@@ -9128,11 +8996,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A35" s="2" t="inlineStr"/>
       <c r="B35" s="2" t="inlineStr">
         <is>
           <t>111001800694</t>
@@ -9381,11 +9245,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="inlineStr"/>
       <c r="B36" s="2" t="inlineStr">
         <is>
           <t>111001800694</t>
@@ -9634,11 +9494,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A37" s="2" t="inlineStr"/>
       <c r="B37" s="2" t="inlineStr">
         <is>
           <t>111001800694</t>
@@ -9887,11 +9743,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A38" s="2" t="inlineStr"/>
       <c r="B38" s="2" t="inlineStr">
         <is>
           <t>111001800694</t>
@@ -10140,11 +9992,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="2" t="inlineStr">
         <is>
           <t>111001800694</t>
@@ -10393,11 +10241,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A40" s="2" t="inlineStr"/>
       <c r="B40" s="2" t="inlineStr">
         <is>
           <t>111001800694</t>
@@ -10646,11 +10490,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A41" s="2" t="inlineStr"/>
       <c r="B41" s="2" t="inlineStr">
         <is>
           <t>111001800694</t>
@@ -10899,11 +10739,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A42" s="2" t="inlineStr"/>
       <c r="B42" s="2" t="inlineStr">
         <is>
           <t>111001800694</t>
@@ -11140,11 +10976,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A43" s="2" t="inlineStr"/>
       <c r="B43" s="2" t="inlineStr">
         <is>
           <t>111001800694</t>
@@ -11385,11 +11217,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A44" s="2" t="inlineStr"/>
       <c r="B44" s="2" t="inlineStr">
         <is>
           <t>111001800694</t>
@@ -11638,11 +11466,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A45" s="2" t="inlineStr"/>
       <c r="B45" s="2" t="inlineStr">
         <is>
           <t>111001800694</t>
@@ -11891,11 +11715,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A46" s="2" t="inlineStr"/>
       <c r="B46" s="2" t="inlineStr">
         <is>
           <t>111001800694</t>
@@ -12144,11 +11964,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A47" s="2" t="inlineStr"/>
       <c r="B47" s="2" t="inlineStr">
         <is>
           <t>111001800694</t>
@@ -12397,11 +12213,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A48" s="2" t="inlineStr"/>
       <c r="B48" s="2" t="inlineStr">
         <is>
           <t>111001800694</t>
@@ -12650,11 +12462,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A49" s="2" t="inlineStr"/>
       <c r="B49" s="2" t="inlineStr">
         <is>
           <t>111001800694</t>
@@ -12903,11 +12711,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A50" s="2" t="inlineStr"/>
       <c r="B50" s="2" t="inlineStr">
         <is>
           <t>111001800694</t>
@@ -13156,11 +12960,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A51" s="2" t="inlineStr"/>
       <c r="B51" s="2" t="inlineStr">
         <is>
           <t>111001800694</t>
@@ -13409,11 +13209,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A52" s="2" t="inlineStr"/>
       <c r="B52" s="2" t="inlineStr">
         <is>
           <t>111001800694</t>
@@ -13662,11 +13458,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A53" s="2" t="inlineStr"/>
       <c r="B53" s="2" t="inlineStr">
         <is>
           <t>111001800694</t>
@@ -13915,11 +13707,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A54" s="2" t="inlineStr"/>
       <c r="B54" s="2" t="inlineStr">
         <is>
           <t>111001800694</t>
@@ -14168,11 +13956,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A55" s="2" t="inlineStr"/>
       <c r="B55" s="2" t="inlineStr">
         <is>
           <t>111001800694</t>
@@ -14417,11 +14201,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A56" s="2" t="inlineStr"/>
       <c r="B56" s="2" t="inlineStr">
         <is>
           <t>111001800694</t>
@@ -14670,11 +14450,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A57" s="2" t="inlineStr"/>
       <c r="B57" s="2" t="inlineStr">
         <is>
           <t>111001800694</t>
